--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-25).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-25).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.709.364,35</t>
-  </si>
-  <si>
-    <t>R$ 9.444,00
-R$ 9.558,45</t>
-  </si>
-  <si>
-    <t>(4.5%)
-(3.3%)</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>(6.2%)</t>
-  </si>
-  <si>
-    <t>249.9%</t>
-  </si>
-  <si>
-    <t>207.4%</t>
+174</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.730.699,26</t>
+  </si>
+  <si>
+    <t>R$ 9.405,97
+R$ 9.557,06</t>
+  </si>
+  <si>
+    <t>(5.2%)
+(3.6%)</t>
+  </si>
+  <si>
+    <t>99.1</t>
+  </si>
+  <si>
+    <t>(6.9%)</t>
+  </si>
+  <si>
+    <t>247.5%</t>
+  </si>
+  <si>
+    <t>205.2%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.6</t>
   </si>
   <si>
-    <t>59.4%</t>
-  </si>
-  <si>
-    <t>14.6%</t>
+    <t>59.5%</t>
+  </si>
+  <si>
+    <t>14.7%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -968,13 +968,13 @@
     <t>21.2</t>
   </si>
   <si>
-    <t>63.2%</t>
-  </si>
-  <si>
-    <t>-R$ 49.445,98</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>63.0%</t>
+  </si>
+  <si>
+    <t>-R$ 52.127,80</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1411,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="7.43" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -1884,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.7200720430107523</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>18.83154</v>
+      </c>
       <c r="AD4" s="8">
         <v>24.065053763440861</v>
       </c>
@@ -2997,10 +2999,10 @@
         <v>0.042857142857142927</v>
       </c>
       <c r="T13" s="6">
-        <v>0.22893612355891904</v>
+        <v>0.21409572147056222</v>
       </c>
       <c r="U13" s="6">
-        <v>-0.11861317085685341</v>
+        <v>-0.13345357294521024</v>
       </c>
       <c r="V13" s="6">
         <v>0.022572979563017986</v>
@@ -4384,7 +4386,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4420,25 +4422,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>10360.030000000001</v>
+      </c>
+      <c r="P24" s="5">
+        <v>10360.030000000001</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.099833869434582612</v>
+      </c>
+      <c r="R24" s="7">
+        <v>116</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.16546762589928055</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0.0054864705990233615</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.33946233746427373</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.016012260582257</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0012772646411255565</v>
+      </c>
+      <c r="X24" s="8">
+        <v>29.949638043478263</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.11956521739130435</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>5.1401176991150441</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>8.5481880434782607</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>20.652355434782606</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.54347826086956519</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-151.90000000000001</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5706,10 +5742,10 @@
         <v>0.44508670520231219</v>
       </c>
       <c r="T34" s="6">
-        <v>0.032492126711404314</v>
+        <v>0.025357440198525268</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.31645865398731748</v>
+        <v>-0.32359334050019656</v>
       </c>
       <c r="V34" s="6">
         <v>0.041501086869012153</v>
@@ -9333,7 +9369,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -9369,11 +9405,21 @@
       <c t="s" r="N63" s="4">
         <v>52</v>
       </c>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="6"/>
+      <c r="O63" s="5">
+        <v>0</v>
+      </c>
+      <c r="P63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R63" s="7">
+        <v>101</v>
+      </c>
+      <c r="S63" s="6">
+        <v>-0.15833333333333333</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
@@ -9381,13 +9427,17 @@
       <c r="X63" s="8"/>
       <c r="Y63" s="6"/>
       <c r="Z63" s="6"/>
-      <c r="AA63" s="8"/>
+      <c r="AA63" s="8">
+        <v>0.19288058252427187</v>
+      </c>
       <c r="AB63" s="8"/>
       <c r="AC63" s="8"/>
       <c r="AD63" s="8"/>
       <c r="AE63" s="6"/>
       <c r="AF63" s="9"/>
-      <c r="AG63" s="5"/>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
       <c r="AH63" s="10">
         <v>3</v>
       </c>
@@ -12528,7 +12578,7 @@
         <v>-101.79000000000001</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12567,7 +12617,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12601,25 +12651,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>8514.7600000000002</v>
+      </c>
+      <c r="P89" s="5">
+        <v>8514.7600000000002</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.37505568876822681</v>
+      </c>
+      <c r="R89" s="7">
+        <v>77</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.4031007751937985</v>
+      </c>
+      <c r="T89" s="6">
+        <v>1.5418251013534143</v>
+      </c>
+      <c r="U89" s="6">
+        <v>1.2038684237723671</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.023229368766706282</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.008330534272251949</v>
+      </c>
+      <c r="X89" s="8">
+        <v>43.087096774193547</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.80645161290322576</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>12.15458375</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>9.4747322580645168</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>32.428493548387095</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.032258064516129031</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-69.799999999999997</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16571,7 +16655,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18534,7 +18618,7 @@
         <v>-274.39999999999998</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20776,7 +20860,7 @@
         <v>100.5</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -27381,7 +27465,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27417,25 +27501,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>2460.1199999999999</v>
+      </c>
+      <c r="P207" s="5">
+        <v>2460.1199999999999</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>27</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>-0.014173698843958832</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.36799383769897404</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.052978513243256427</v>
+      </c>
+      <c r="W207" s="6">
+        <v>-0.0052015755329008345</v>
+      </c>
+      <c r="X207" s="8">
+        <v>26.792594444444447</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>7.8086407407407412</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>6.9675944444444449</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>14.753703</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>21.717594444444444</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.72222222222222221</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-2460.1199999999999</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>
